--- a/Side Bar Files/GWD Data/Metallic PH.xlsx
+++ b/Side Bar Files/GWD Data/Metallic PH.xlsx
@@ -483,23 +483,33 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="177" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -606,6 +616,7 @@
       <sheetName val="3 Core Cable PRICE"/>
       <sheetName val="ARS Filter Media"/>
       <sheetName val="BW Casing Pipes"/>
+      <sheetName val="Electrical Essentials"/>
       <sheetName val="GI on Wall PRICE"/>
       <sheetName val="GI wo Trench"/>
       <sheetName val="GI With Trench PRICE"/>
@@ -613,16 +624,19 @@
       <sheetName val="Gravel for TWC"/>
       <sheetName val="Gutter&amp;Clamp"/>
       <sheetName val="HDPE Pipe PRICE"/>
+      <sheetName val="HP Erection and Pullout"/>
       <sheetName val="HP Repair Labour"/>
       <sheetName val="HP Repair Spares"/>
       <sheetName val="Hydrants"/>
       <sheetName val="Iron Structure"/>
+      <sheetName val="Lock"/>
       <sheetName val="Metallic PH"/>
       <sheetName val="Motor Starter GWD"/>
       <sheetName val="Motor Starter Monoblock"/>
       <sheetName val="Motor Starter PRICE"/>
       <sheetName val="Other Fittings PRICE"/>
       <sheetName val="Panel Board"/>
+      <sheetName val="Pump Cover"/>
       <sheetName val="Pump Erection "/>
       <sheetName val="Pump Pullout"/>
       <sheetName val="PVC Fittings"/>
@@ -683,6 +697,10 @@
       <sheetData sheetId="37"/>
       <sheetData sheetId="38"/>
       <sheetData sheetId="39"/>
+      <sheetData sheetId="40"/>
+      <sheetData sheetId="41"/>
+      <sheetData sheetId="42"/>
+      <sheetData sheetId="43"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -984,7 +1002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDBF5B9F-5462-4819-A859-52B9D582B9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F96DD977-6AE5-4576-A9C9-98568293B9A7}">
   <dimension ref="A1:J63"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/Metallic PH.xlsx
+++ b/Side Bar Files/GWD Data/Metallic PH.xlsx
@@ -438,25 +438,11 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment/>
       <protection/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -522,11 +508,11 @@
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="15" builtinId="5"/>
-    <cellStyle name="Currency" xfId="16" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
-    <cellStyle name="Comma" xfId="18" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="3" builtinId="7"/>
+    <cellStyle name="Comma" xfId="4" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="5" builtinId="6"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -623,7 +609,6 @@
       <sheetName val="GI Works"/>
       <sheetName val="Gravel for TWC"/>
       <sheetName val="Gutter&amp;Clamp"/>
-      <sheetName val="HDPE Pipe PRICE"/>
       <sheetName val="HP Erection and Pullout"/>
       <sheetName val="HP Repair Labour"/>
       <sheetName val="HP Repair Spares"/>
@@ -643,9 +628,11 @@
       <sheetName val="PVC Fittings PRICE"/>
       <sheetName val="PVC on Wall (Concealed) PRICE"/>
       <sheetName val="PVC on Wall PRICE"/>
+      <sheetName val="PVC on Wall"/>
+      <sheetName val="PVC wo Trench PRICE"/>
       <sheetName val="PVC wo Trench"/>
+      <sheetName val="PVC With Trench PRICE"/>
       <sheetName val="PVC With Trench"/>
-      <sheetName val="PVC With Trench PRICE"/>
       <sheetName val="Scaffolding"/>
       <sheetName val="Services"/>
       <sheetName val="TW Casing Pipes"/>
@@ -654,6 +641,9 @@
       <sheetName val="Water Tank"/>
       <sheetName val="Well Protection"/>
       <sheetName val="WTP"/>
+      <sheetName val="Derived"/>
+      <sheetName val="LMR"/>
+      <sheetName val="PAMR39"/>
       <sheetName val="ZCost Index"/>
     </sheetNames>
     <sheetDataSet>
@@ -701,6 +691,10 @@
       <sheetData sheetId="41"/>
       <sheetData sheetId="42"/>
       <sheetData sheetId="43"/>
+      <sheetData sheetId="44"/>
+      <sheetData sheetId="45"/>
+      <sheetData sheetId="46"/>
+      <sheetData sheetId="47"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1002,7 +996,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F96DD977-6AE5-4576-A9C9-98568293B9A7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B69FE150-90C1-4F5A-9CB2-FA275875BAA6}">
   <dimension ref="A1:J63"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/Metallic PH.xlsx
+++ b/Side Bar Files/GWD Data/Metallic PH.xlsx
@@ -996,7 +996,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B69FE150-90C1-4F5A-9CB2-FA275875BAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E29345A2-B504-412B-8E58-66A8FE62BAA6}">
   <dimension ref="A1:J63"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/Metallic PH.xlsx
+++ b/Side Bar Files/GWD Data/Metallic PH.xlsx
@@ -641,10 +641,10 @@
       <sheetName val="Water Tank"/>
       <sheetName val="Well Protection"/>
       <sheetName val="WTP"/>
-      <sheetName val="Derived"/>
-      <sheetName val="LMR"/>
-      <sheetName val="PAMR39"/>
-      <sheetName val="ZCost Index"/>
+      <sheetName val="zCost Index"/>
+      <sheetName val="zDerived"/>
+      <sheetName val="zLMR"/>
+      <sheetName val="zPAMR39"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -996,7 +996,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E29345A2-B504-412B-8E58-66A8FE62BAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F22AECB-AD01-4044-B5F5-B183F4A7BAA6}">
   <dimension ref="A1:J63"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
